--- a/cancer_screening_test_members.xlsx
+++ b/cancer_screening_test_members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajohn\OneDrive\Desktop\knowledge-graph-AIAgents\Knowledge-Graph-AIAgent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACAF3CB-D963-491C-B577-80D34C33B7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4EF894-E4D0-446F-984C-5AD4FF1A59B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -313,19 +313,19 @@
     <t>Influenza|2025;Pneumococcal|2024;Shingles|2024;Tdap|2022</t>
   </si>
   <si>
-    <t>Markliny</t>
-  </si>
-  <si>
-    <t>Patelly</t>
-  </si>
-  <si>
-    <t>Emikinny</t>
-  </si>
-  <si>
-    <t>Kan Williams</t>
-  </si>
-  <si>
-    <t>Lindally</t>
+    <t>hencika</t>
+  </si>
+  <si>
+    <t>kitica</t>
+  </si>
+  <si>
+    <t>Emilika</t>
+  </si>
+  <si>
+    <t>Josh Hazelwood</t>
+  </si>
+  <si>
+    <t>rithica</t>
   </si>
 </sst>
 </file>

--- a/cancer_screening_test_members.xlsx
+++ b/cancer_screening_test_members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajohn\OneDrive\Desktop\knowledge-graph-AIAgents\Knowledge-Graph-AIAgent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4EF894-E4D0-446F-984C-5AD4FF1A59B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC83B95-A314-4395-A0ED-D5B8200025C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -313,19 +313,19 @@
     <t>Influenza|2025;Pneumococcal|2024;Shingles|2024;Tdap|2022</t>
   </si>
   <si>
-    <t>hencika</t>
-  </si>
-  <si>
-    <t>kitica</t>
-  </si>
-  <si>
-    <t>Emilika</t>
-  </si>
-  <si>
-    <t>Josh Hazelwood</t>
-  </si>
-  <si>
-    <t>rithica</t>
+    <t>Tanica</t>
+  </si>
+  <si>
+    <t>hepsi</t>
+  </si>
+  <si>
+    <t>kinly</t>
+  </si>
+  <si>
+    <t>robin</t>
+  </si>
+  <si>
+    <t>petrica</t>
   </si>
 </sst>
 </file>
